--- a/tests/testdata/excel/2024/見積/A社.xlsx
+++ b/tests/testdata/excel/2024/見積/A社.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{239437CF-E6BF-421C-A2D9-1857CA7DD1E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{04228D97-4C5C-4BB8-8A87-F8D7749A53B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{C6470E87-60FE-4649-99E6-6DF0DE0F4B58}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{253317D2-F4DB-4720-8E15-0876A17BE292}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -464,7 +464,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35204446-F200-48FF-9E44-6284416EE533}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB0AB371-74F8-4920-BE06-FEF86DE0A48E}">
   <dimension ref="B2:C4"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -493,7 +493,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EDE926D-FE80-40E6-A7BB-ABA68AEC064C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F51CEF82-1C08-4642-B1F1-AB25000BAF9F}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>

--- a/tests/testdata/excel/2024/見積/A社.xlsx
+++ b/tests/testdata/excel/2024/見積/A社.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{04228D97-4C5C-4BB8-8A87-F8D7749A53B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE250122-8AF5-40AD-A658-0E433E2FF5F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{253317D2-F4DB-4720-8E15-0876A17BE292}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{FC32F956-17DA-49FE-9250-DC9DD779787C}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -464,7 +464,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB0AB371-74F8-4920-BE06-FEF86DE0A48E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C25E6086-487C-47FB-9997-7B414772807E}">
   <dimension ref="B2:C4"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -493,7 +493,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F51CEF82-1C08-4642-B1F1-AB25000BAF9F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F27A0FA-B546-4C5F-B75A-0D8C1CB5166F}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
